--- a/branches/feat/comparison-demo/all-profiles.xlsx
+++ b/branches/feat/comparison-demo/all-profiles.xlsx
@@ -66,7 +66,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-30T14:24:13+00:00</t>
+    <t>2026-07-30T14:28:24+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/feat/comparison-demo/all-profiles.xlsx
+++ b/branches/feat/comparison-demo/all-profiles.xlsx
@@ -66,7 +66,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-30T14:28:24+00:00</t>
+    <t>2026-07-30T14:33:24+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/feat/comparison-demo/all-profiles.xlsx
+++ b/branches/feat/comparison-demo/all-profiles.xlsx
@@ -66,7 +66,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-30T14:33:24+00:00</t>
+    <t>2026-07-30T14:50:59+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/feat/comparison-demo/all-profiles.xlsx
+++ b/branches/feat/comparison-demo/all-profiles.xlsx
@@ -66,7 +66,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-30T14:50:59+00:00</t>
+    <t>2026-07-30T14:58:38+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
